--- a/PINOUT_Estrella de la muerte.xlsx
+++ b/PINOUT_Estrella de la muerte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\razer\OneDrive\Documentos\GitHub\Proyecto1-Digital2-Grupo7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC706598-BA0E-4B42-8549-4C2C4E6EC54E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1314C352-2FD5-4407-BB96-BBB497251905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38CA4A19-C4A4-B443-AA8F-BED2C3120EBF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="107">
   <si>
     <t>D13</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>SENSOR DE COLOR</t>
+  </si>
+  <si>
+    <t>S</t>
   </si>
 </sst>
 </file>
@@ -483,7 +486,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -507,31 +510,30 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -553,16 +555,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>956733</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>143934</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>113802</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>237066</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>29136</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -585,8 +587,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9512300" y="241300"/>
-          <a:ext cx="7112000" cy="5968502"/>
+          <a:off x="956733" y="16717434"/>
+          <a:ext cx="7281333" cy="5600202"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1014,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D50DAB75-1D4A-1F4B-BA8C-006C9BBD0D11}">
-  <dimension ref="A2:M80"/>
+  <dimension ref="A2:R80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.09765625" customWidth="1"/>
@@ -1028,57 +1030,57 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
     </row>
     <row r="3" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
     </row>
     <row r="4" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
     </row>
     <row r="5" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
       <c r="K8" s="5" t="s">
         <v>51</v>
       </c>
@@ -1111,10 +1113,10 @@
       <c r="D10" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="14"/>
+      <c r="F10" s="17"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
@@ -1126,7 +1128,7 @@
       <c r="K10" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="L10" s="18" t="s">
+      <c r="L10" s="12" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1135,10 +1137,10 @@
         <v>68</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="15"/>
+      <c r="F11" s="13"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
@@ -1150,7 +1152,7 @@
       <c r="K11" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="L11" s="18"/>
+      <c r="L11" s="12"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
@@ -1174,7 +1176,7 @@
       <c r="K12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L12" s="18"/>
+      <c r="L12" s="12"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
@@ -1198,7 +1200,7 @@
       <c r="K13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L13" s="18"/>
+      <c r="L13" s="12"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
@@ -1222,7 +1224,7 @@
       <c r="K14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L14" s="18"/>
+      <c r="L14" s="12"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
@@ -1246,7 +1248,7 @@
       <c r="K15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="L15" s="18"/>
+      <c r="L15" s="12"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
@@ -1275,9 +1277,9 @@
       <c r="K16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L16" s="18"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L16" s="12"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="C17" s="7" t="s">
         <v>67</v>
@@ -1302,9 +1304,9 @@
       <c r="K17" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L17" s="18"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L17" s="12"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>53</v>
       </c>
@@ -1326,9 +1328,9 @@
       <c r="K18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="L18" s="18"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L18" s="12"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>73</v>
       </c>
@@ -1350,30 +1352,33 @@
       <c r="K19" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="L19" s="18"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L19" s="12"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>70</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="11"/>
+      <c r="F20" s="14"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="16" t="s">
+      <c r="I20" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="J20" s="16"/>
+      <c r="J20" s="15"/>
       <c r="K20" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="R20" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="D21" s="3"/>
       <c r="E21" s="4" t="s">
@@ -1392,14 +1397,14 @@
       </c>
       <c r="K21" s="3"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D22" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="16"/>
+      <c r="F22" s="15"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
@@ -1412,12 +1417,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D23" s="3"/>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="17"/>
+      <c r="F23" s="18"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
@@ -1430,7 +1435,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B24" s="10"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -1439,61 +1444,58 @@
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M25" s="19"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D31" s="13" t="s">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D31" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D36" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
       <c r="K36" s="5" t="s">
         <v>51</v>
       </c>
@@ -1518,10 +1520,10 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D38" s="3"/>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="F38" s="14"/>
+      <c r="F38" s="17"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
@@ -1542,10 +1544,10 @@
         <v>54</v>
       </c>
       <c r="D39" s="3"/>
-      <c r="E39" s="15" t="s">
+      <c r="E39" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F39" s="15"/>
+      <c r="F39" s="13"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2" t="s">
@@ -1747,16 +1749,16 @@
       <c r="D48" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F48" s="11"/>
+      <c r="F48" s="14"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
-      <c r="I48" s="16" t="s">
+      <c r="I48" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="J48" s="16"/>
+      <c r="J48" s="15"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
@@ -1786,10 +1788,10 @@
       <c r="D50" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E50" s="16" t="s">
+      <c r="E50" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F50" s="16"/>
+      <c r="F50" s="15"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2" t="s">
@@ -1805,10 +1807,10 @@
         <v>98</v>
       </c>
       <c r="D51" s="3"/>
-      <c r="E51" s="17" t="s">
+      <c r="E51" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F51" s="17"/>
+      <c r="F51" s="18"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2" t="s">
@@ -1856,57 +1858,57 @@
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D58" s="13" t="s">
+      <c r="D58" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
-      <c r="K58" s="13"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="11"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
-      <c r="K59" s="13"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
+      <c r="K59" s="11"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="11"/>
+      <c r="K60" s="11"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="13"/>
-      <c r="J61" s="13"/>
-      <c r="K61" s="13"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
+      <c r="K61" s="11"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D64" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
       <c r="G64" s="6"/>
       <c r="H64" s="6"/>
-      <c r="I64" s="12"/>
-      <c r="J64" s="12"/>
+      <c r="I64" s="16"/>
+      <c r="J64" s="16"/>
       <c r="K64" s="5" t="s">
         <v>51</v>
       </c>
@@ -1931,10 +1933,10 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D66" s="3"/>
-      <c r="E66" s="14" t="s">
+      <c r="E66" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="F66" s="14"/>
+      <c r="F66" s="17"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2" t="s">
@@ -1953,10 +1955,10 @@
         <v>54</v>
       </c>
       <c r="D67" s="3"/>
-      <c r="E67" s="15" t="s">
+      <c r="E67" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F67" s="15"/>
+      <c r="F67" s="13"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2" t="s">
@@ -2157,16 +2159,16 @@
       <c r="D76" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E76" s="11" t="s">
+      <c r="E76" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F76" s="11"/>
+      <c r="F76" s="14"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
-      <c r="I76" s="16" t="s">
+      <c r="I76" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="J76" s="16"/>
+      <c r="J76" s="15"/>
       <c r="K76" s="3" t="s">
         <v>55</v>
       </c>
@@ -2193,10 +2195,10 @@
       <c r="D78" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E78" s="16" t="s">
+      <c r="E78" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F78" s="16"/>
+      <c r="F78" s="15"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2" t="s">
@@ -2209,10 +2211,10 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D79" s="3"/>
-      <c r="E79" s="17" t="s">
+      <c r="E79" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F79" s="17"/>
+      <c r="F79" s="18"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="2" t="s">
@@ -2233,6 +2235,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="D2:K5"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="E66:F66"/>
     <mergeCell ref="D31:K34"/>
     <mergeCell ref="D58:K61"/>
     <mergeCell ref="L10:L19"/>
@@ -2249,18 +2263,6 @@
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="I20:J20"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="D2:K5"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
